--- a/data/HCA_multinomial_regression.xlsx
+++ b/data/HCA_multinomial_regression.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="296">
   <si>
     <t>Variable</t>
   </si>
@@ -66,826 +66,829 @@
     <t>Total Population</t>
   </si>
   <si>
-    <t>5.286***</t>
-  </si>
-  <si>
-    <t>1.464</t>
-  </si>
-  <si>
-    <t>2.349</t>
-  </si>
-  <si>
-    <t>1.467</t>
-  </si>
-  <si>
-    <t>-11.372***</t>
-  </si>
-  <si>
-    <t>2.371</t>
-  </si>
-  <si>
-    <t>-8.968**</t>
-  </si>
-  <si>
-    <t>2.943</t>
-  </si>
-  <si>
-    <t>0.868</t>
-  </si>
-  <si>
-    <t>1.359</t>
-  </si>
-  <si>
-    <t>-3.042</t>
-  </si>
-  <si>
-    <t>1.614</t>
-  </si>
-  <si>
-    <t>-3.203</t>
-  </si>
-  <si>
-    <t>1.770</t>
+    <t>10.188*</t>
+  </si>
+  <si>
+    <t>4.477</t>
+  </si>
+  <si>
+    <t>15.730***</t>
+  </si>
+  <si>
+    <t>4.545</t>
+  </si>
+  <si>
+    <t>18.241***</t>
+  </si>
+  <si>
+    <t>4.453</t>
+  </si>
+  <si>
+    <t>19.112***</t>
+  </si>
+  <si>
+    <t>4.502</t>
+  </si>
+  <si>
+    <t>18.522***</t>
+  </si>
+  <si>
+    <t>4.587</t>
+  </si>
+  <si>
+    <t>23.562***</t>
+  </si>
+  <si>
+    <t>4.524</t>
+  </si>
+  <si>
+    <t>15.922**</t>
+  </si>
+  <si>
+    <t>4.993</t>
   </si>
   <si>
     <t>Population Density</t>
   </si>
   <si>
-    <t>0.701</t>
-  </si>
-  <si>
-    <t>0.607</t>
-  </si>
-  <si>
-    <t>0.388</t>
-  </si>
-  <si>
-    <t>0.646</t>
-  </si>
-  <si>
-    <t>0.074</t>
-  </si>
-  <si>
-    <t>0.659</t>
-  </si>
-  <si>
-    <t>0.032</t>
-  </si>
-  <si>
-    <t>0.807</t>
+    <t>-0.653</t>
+  </si>
+  <si>
+    <t>0.630</t>
+  </si>
+  <si>
+    <t>0.220</t>
+  </si>
+  <si>
+    <t>0.642</t>
+  </si>
+  <si>
+    <t>-0.318</t>
+  </si>
+  <si>
+    <t>-0.102</t>
+  </si>
+  <si>
+    <t>0.655</t>
+  </si>
+  <si>
+    <t>-0.770</t>
+  </si>
+  <si>
+    <t>0.776</t>
+  </si>
+  <si>
+    <t>-0.136</t>
+  </si>
+  <si>
+    <t>0.671</t>
+  </si>
+  <si>
+    <t>-0.302</t>
+  </si>
+  <si>
+    <t>0.903</t>
+  </si>
+  <si>
+    <t>Bachelor's Degree or Higher</t>
+  </si>
+  <si>
+    <t>-0.254</t>
   </si>
   <si>
     <t>0.276</t>
   </si>
   <si>
-    <t>0.577</t>
-  </si>
-  <si>
-    <t>0.720</t>
-  </si>
-  <si>
-    <t>0.592</t>
-  </si>
-  <si>
-    <t>1.416*</t>
-  </si>
-  <si>
-    <t>0.595</t>
-  </si>
-  <si>
-    <t>Bachelor's Degree or Higher</t>
-  </si>
-  <si>
-    <t>0.523</t>
-  </si>
-  <si>
-    <t>0.474</t>
-  </si>
-  <si>
-    <t>-0.440</t>
-  </si>
-  <si>
-    <t>0.417</t>
-  </si>
-  <si>
-    <t>-1.245***</t>
-  </si>
-  <si>
-    <t>0.346</t>
-  </si>
-  <si>
-    <t>0.798*</t>
-  </si>
-  <si>
-    <t>0.334</t>
+    <t>-0.051</t>
+  </si>
+  <si>
+    <t>0.343</t>
+  </si>
+  <si>
+    <t>1.543***</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>0.101</t>
+  </si>
+  <si>
+    <t>0.351</t>
+  </si>
+  <si>
+    <t>1.035**</t>
+  </si>
+  <si>
+    <t>0.397</t>
+  </si>
+  <si>
+    <t>1.724***</t>
+  </si>
+  <si>
+    <t>0.471</t>
+  </si>
+  <si>
+    <t>0.564</t>
+  </si>
+  <si>
+    <t>0.466</t>
+  </si>
+  <si>
+    <t>Median Household Income</t>
+  </si>
+  <si>
+    <t>-0.258</t>
+  </si>
+  <si>
+    <t>0.342</t>
+  </si>
+  <si>
+    <t>-0.755</t>
+  </si>
+  <si>
+    <t>0.433</t>
+  </si>
+  <si>
+    <t>-1.768***</t>
+  </si>
+  <si>
+    <t>0.379</t>
+  </si>
+  <si>
+    <t>-0.592</t>
+  </si>
+  <si>
+    <t>0.438</t>
+  </si>
+  <si>
+    <t>-1.965***</t>
+  </si>
+  <si>
+    <t>0.571</t>
+  </si>
+  <si>
+    <t>-1.277*</t>
+  </si>
+  <si>
+    <t>0.624</t>
+  </si>
+  <si>
+    <t>-1.189</t>
+  </si>
+  <si>
+    <t>0.644</t>
+  </si>
+  <si>
+    <t>Poverty Rate</t>
+  </si>
+  <si>
+    <t>0.119</t>
+  </si>
+  <si>
+    <t>0.279</t>
+  </si>
+  <si>
+    <t>-0.189</t>
+  </si>
+  <si>
+    <t>0.372</t>
+  </si>
+  <si>
+    <t>-0.074</t>
+  </si>
+  <si>
+    <t>0.320</t>
+  </si>
+  <si>
+    <t>-0.138</t>
+  </si>
+  <si>
+    <t>0.394</t>
+  </si>
+  <si>
+    <t>-0.762</t>
+  </si>
+  <si>
+    <t>0.452</t>
+  </si>
+  <si>
+    <t>0.653</t>
+  </si>
+  <si>
+    <t>-0.577</t>
+  </si>
+  <si>
+    <t>0.558</t>
+  </si>
+  <si>
+    <t>Unemployment Rate</t>
+  </si>
+  <si>
+    <t>0.102</t>
+  </si>
+  <si>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>-0.182</t>
+  </si>
+  <si>
+    <t>0.232</t>
+  </si>
+  <si>
+    <t>0.130</t>
+  </si>
+  <si>
+    <t>0.197</t>
+  </si>
+  <si>
+    <t>-0.097</t>
+  </si>
+  <si>
+    <t>0.249</t>
+  </si>
+  <si>
+    <t>0.269</t>
+  </si>
+  <si>
+    <t>0.278</t>
+  </si>
+  <si>
+    <t>0.235</t>
+  </si>
+  <si>
+    <t>0.395</t>
+  </si>
+  <si>
+    <t>-0.411</t>
+  </si>
+  <si>
+    <t>0.340</t>
+  </si>
+  <si>
+    <t>Non-Hispanic Black</t>
+  </si>
+  <si>
+    <t>0.270</t>
+  </si>
+  <si>
+    <t>0.254</t>
+  </si>
+  <si>
+    <t>0.315</t>
+  </si>
+  <si>
+    <t>0.303</t>
+  </si>
+  <si>
+    <t>0.360</t>
+  </si>
+  <si>
+    <t>0.484</t>
+  </si>
+  <si>
+    <t>0.299</t>
+  </si>
+  <si>
+    <t>1.495***</t>
   </si>
   <si>
     <t>0.347</t>
   </si>
   <si>
-    <t>0.324</t>
-  </si>
-  <si>
-    <t>-0.897**</t>
-  </si>
-  <si>
-    <t>0.338</t>
-  </si>
-  <si>
-    <t>-0.393</t>
-  </si>
-  <si>
-    <t>0.354</t>
-  </si>
-  <si>
-    <t>Median Household Income</t>
-  </si>
-  <si>
-    <t>0.758</t>
-  </si>
-  <si>
-    <t>0.712</t>
-  </si>
-  <si>
-    <t>0.792</t>
-  </si>
-  <si>
-    <t>0.636</t>
-  </si>
-  <si>
-    <t>1.772***</t>
-  </si>
-  <si>
-    <t>0.527</t>
-  </si>
-  <si>
-    <t>-0.076</t>
-  </si>
-  <si>
-    <t>0.549</t>
-  </si>
-  <si>
-    <t>0.518</t>
-  </si>
-  <si>
-    <t>1.387**</t>
-  </si>
-  <si>
-    <t>0.657</t>
-  </si>
-  <si>
-    <t>0.565</t>
-  </si>
-  <si>
-    <t>Poverty Rate</t>
-  </si>
-  <si>
-    <t>1.406*</t>
-  </si>
-  <si>
-    <t>0.704</t>
-  </si>
-  <si>
-    <t>0.568</t>
-  </si>
-  <si>
-    <t>0.521</t>
-  </si>
-  <si>
-    <t>0.858*</t>
-  </si>
-  <si>
-    <t>0.398</t>
-  </si>
-  <si>
     <t>0.472</t>
   </si>
   <si>
-    <t>0.443</t>
-  </si>
-  <si>
-    <t>1.013*</t>
-  </si>
-  <si>
-    <t>0.434</t>
-  </si>
-  <si>
-    <t>0.520</t>
-  </si>
-  <si>
-    <t>0.415</t>
-  </si>
-  <si>
-    <t>0.585</t>
-  </si>
-  <si>
-    <t>0.469</t>
-  </si>
-  <si>
-    <t>Unemployment Rate</t>
-  </si>
-  <si>
-    <t>-0.147</t>
-  </si>
-  <si>
-    <t>0.426</t>
-  </si>
-  <si>
-    <t>-0.807*</t>
+    <t>0.428</t>
+  </si>
+  <si>
+    <t>0.940*</t>
+  </si>
+  <si>
+    <t>0.368</t>
+  </si>
+  <si>
+    <t>Hispanic or Latino</t>
+  </si>
+  <si>
+    <t>0.713*</t>
+  </si>
+  <si>
+    <t>0.286</t>
+  </si>
+  <si>
+    <t>0.902**</t>
+  </si>
+  <si>
+    <t>0.304</t>
+  </si>
+  <si>
+    <t>-0.523</t>
+  </si>
+  <si>
+    <t>0.461</t>
+  </si>
+  <si>
+    <t>1.369***</t>
+  </si>
+  <si>
+    <t>0.387</t>
+  </si>
+  <si>
+    <t>0.111</t>
+  </si>
+  <si>
+    <t>0.525</t>
+  </si>
+  <si>
+    <t>0.261</t>
+  </si>
+  <si>
+    <t>0.586</t>
+  </si>
+  <si>
+    <t>Non-Hispanic Asian</t>
+  </si>
+  <si>
+    <t>2.035*</t>
+  </si>
+  <si>
+    <t>0.847</t>
+  </si>
+  <si>
+    <t>2.046*</t>
+  </si>
+  <si>
+    <t>0.863</t>
+  </si>
+  <si>
+    <t>2.217**</t>
+  </si>
+  <si>
+    <t>0.852</t>
+  </si>
+  <si>
+    <t>1.979*</t>
+  </si>
+  <si>
+    <t>0.874</t>
+  </si>
+  <si>
+    <t>2.650**</t>
+  </si>
+  <si>
+    <t>0.870</t>
+  </si>
+  <si>
+    <t>2.311**</t>
+  </si>
+  <si>
+    <t>0.880</t>
+  </si>
+  <si>
+    <t>1.398</t>
+  </si>
+  <si>
+    <t>1.214</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>4.371***</t>
+  </si>
+  <si>
+    <t>1.167</t>
+  </si>
+  <si>
+    <t>4.707***</t>
+  </si>
+  <si>
+    <t>1.174</t>
+  </si>
+  <si>
+    <t>6.082***</t>
+  </si>
+  <si>
+    <t>1.156</t>
+  </si>
+  <si>
+    <t>5.003***</t>
+  </si>
+  <si>
+    <t>1.169</t>
+  </si>
+  <si>
+    <t>3.750**</t>
+  </si>
+  <si>
+    <t>1.198</t>
+  </si>
+  <si>
+    <t>3.617**</t>
+  </si>
+  <si>
+    <t>1.210</t>
+  </si>
+  <si>
+    <t>3.290**</t>
+  </si>
+  <si>
+    <t>1.260</t>
+  </si>
+  <si>
+    <t>Cluster</t>
+  </si>
+  <si>
+    <t>Predictor</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>95% CI</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>Cluster 2 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[4.109, 171985374.640]</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>Cluster 3 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[917.635, 50145769957.986]</t>
+  </si>
+  <si>
+    <t>&lt; .001</t>
+  </si>
+  <si>
+    <t>Cluster 4 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[13536.161, 515745879742.431]</t>
+  </si>
+  <si>
+    <t>Cluster 5 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[29380.310, 1356487833544.473]</t>
+  </si>
+  <si>
+    <t>Cluster 6 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[13786.981, 888250824431.797]</t>
+  </si>
+  <si>
+    <t>Cluster 7 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[2409572.732, 121269929590992.156]</t>
+  </si>
+  <si>
+    <t>Cluster 8 vs. Cluster 1</t>
+  </si>
+  <si>
+    <t>[462.072, 146205645729.889]</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>[0.151, 1.789]</t>
+  </si>
+  <si>
+    <t>0.300</t>
+  </si>
+  <si>
+    <t>[0.354, 4.386]</t>
+  </si>
+  <si>
+    <t>0.732</t>
+  </si>
+  <si>
+    <t>[0.212, 2.501]</t>
+  </si>
+  <si>
+    <t>0.613</t>
+  </si>
+  <si>
+    <t>[0.250, 3.260]</t>
+  </si>
+  <si>
+    <t>0.876</t>
+  </si>
+  <si>
+    <t>[0.101, 2.119]</t>
+  </si>
+  <si>
+    <t>0.321</t>
+  </si>
+  <si>
+    <t>[0.234, 3.252]</t>
+  </si>
+  <si>
+    <t>0.839</t>
+  </si>
+  <si>
+    <t>[0.126, 4.340]</t>
+  </si>
+  <si>
+    <t>0.738</t>
+  </si>
+  <si>
+    <t>[0.452, 1.332]</t>
+  </si>
+  <si>
+    <t>0.358</t>
+  </si>
+  <si>
+    <t>[0.485, 1.861]</t>
+  </si>
+  <si>
+    <t>0.881</t>
+  </si>
+  <si>
+    <t>[2.661, 8.227]</t>
+  </si>
+  <si>
+    <t>[0.556, 2.201]</t>
+  </si>
+  <si>
+    <t>0.774</t>
+  </si>
+  <si>
+    <t>[1.293, 6.130]</t>
+  </si>
+  <si>
+    <t>0.009</t>
+  </si>
+  <si>
+    <t>[2.227, 14.114]</t>
+  </si>
+  <si>
+    <t>[0.705, 4.381]</t>
+  </si>
+  <si>
+    <t>0.226</t>
+  </si>
+  <si>
+    <t>[0.395, 1.510]</t>
+  </si>
+  <si>
+    <t>0.451</t>
+  </si>
+  <si>
+    <t>[0.201, 1.098]</t>
+  </si>
+  <si>
+    <t>0.082</t>
+  </si>
+  <si>
+    <t>[0.081, 0.359]</t>
+  </si>
+  <si>
+    <t>[0.234, 1.305]</t>
+  </si>
+  <si>
+    <t>0.177</t>
+  </si>
+  <si>
+    <t>[0.046, 0.429]</t>
+  </si>
+  <si>
+    <t>[0.082, 0.947]</t>
+  </si>
+  <si>
+    <t>0.041</t>
+  </si>
+  <si>
+    <t>[0.086, 1.076]</t>
+  </si>
+  <si>
+    <t>0.065</t>
+  </si>
+  <si>
+    <t>[0.652, 1.946]</t>
+  </si>
+  <si>
+    <t>0.670</t>
+  </si>
+  <si>
+    <t>[0.399, 1.716]</t>
+  </si>
+  <si>
+    <t>0.611</t>
+  </si>
+  <si>
+    <t>[0.496, 1.739]</t>
+  </si>
+  <si>
+    <t>0.816</t>
+  </si>
+  <si>
+    <t>[0.402, 1.886]</t>
+  </si>
+  <si>
+    <t>0.726</t>
+  </si>
+  <si>
+    <t>[0.192, 1.132]</t>
+  </si>
+  <si>
+    <t>0.092</t>
+  </si>
+  <si>
+    <t>[0.489, 6.321]</t>
+  </si>
+  <si>
+    <t>[0.188, 1.676]</t>
+  </si>
+  <si>
+    <t>0.301</t>
+  </si>
+  <si>
+    <t>[0.780, 1.573]</t>
+  </si>
+  <si>
+    <t>0.567</t>
+  </si>
+  <si>
+    <t>[0.529, 1.314]</t>
+  </si>
+  <si>
+    <t>0.431</t>
+  </si>
+  <si>
+    <t>[0.774, 1.676]</t>
+  </si>
+  <si>
+    <t>0.510</t>
+  </si>
+  <si>
+    <t>[0.557, 1.479]</t>
+  </si>
+  <si>
+    <t>0.697</t>
+  </si>
+  <si>
+    <t>[0.759, 2.257]</t>
   </si>
   <si>
     <t>0.332</t>
   </si>
   <si>
-    <t>-0.151</t>
-  </si>
-  <si>
-    <t>0.243</t>
-  </si>
-  <si>
-    <t>-0.114</t>
-  </si>
-  <si>
-    <t>0.263</t>
-  </si>
-  <si>
-    <t>0.255</t>
-  </si>
-  <si>
-    <t>-0.306</t>
-  </si>
-  <si>
-    <t>0.252</t>
-  </si>
-  <si>
-    <t>-0.498</t>
-  </si>
-  <si>
-    <t>0.281</t>
-  </si>
-  <si>
-    <t>Non-Hispanic Black</t>
-  </si>
-  <si>
-    <t>-1.266**</t>
-  </si>
-  <si>
-    <t>-0.549</t>
-  </si>
-  <si>
-    <t>0.316</t>
-  </si>
-  <si>
-    <t>-1.135***</t>
-  </si>
-  <si>
-    <t>0.273</t>
-  </si>
-  <si>
-    <t>-1.075***</t>
-  </si>
-  <si>
-    <t>0.308</t>
-  </si>
-  <si>
-    <t>-1.320***</t>
-  </si>
-  <si>
-    <t>0.298</t>
-  </si>
-  <si>
-    <t>-1.153***</t>
-  </si>
-  <si>
-    <t>-1.214***</t>
-  </si>
-  <si>
-    <t>0.315</t>
-  </si>
-  <si>
-    <t>Hispanic or Latino</t>
-  </si>
-  <si>
-    <t>-1.263**</t>
-  </si>
-  <si>
-    <t>0.484</t>
-  </si>
-  <si>
-    <t>-1.355**</t>
-  </si>
-  <si>
-    <t>0.498</t>
-  </si>
-  <si>
-    <t>-0.566*</t>
-  </si>
-  <si>
-    <t>-0.539</t>
-  </si>
-  <si>
-    <t>0.319</t>
-  </si>
-  <si>
-    <t>-0.491</t>
+    <t>[0.583, 2.743]</t>
+  </si>
+  <si>
+    <t>0.552</t>
+  </si>
+  <si>
+    <t>[0.340, 1.291]</t>
+  </si>
+  <si>
+    <t>0.227</t>
+  </si>
+  <si>
+    <t>[0.796, 2.155]</t>
   </si>
   <si>
     <t>0.287</t>
   </si>
   <si>
-    <t>-1.512***</t>
-  </si>
-  <si>
-    <t>0.335</t>
-  </si>
-  <si>
-    <t>-0.775*</t>
-  </si>
-  <si>
-    <t>0.331</t>
-  </si>
-  <si>
-    <t>Non-Hispanic Asian</t>
-  </si>
-  <si>
-    <t>-0.283</t>
-  </si>
-  <si>
-    <t>0.310</t>
-  </si>
-  <si>
-    <t>-0.553</t>
-  </si>
-  <si>
-    <t>0.449</t>
-  </si>
-  <si>
-    <t>-0.592*</t>
-  </si>
-  <si>
-    <t>0.247</t>
-  </si>
-  <si>
-    <t>-0.471</t>
-  </si>
-  <si>
-    <t>-0.583*</t>
-  </si>
-  <si>
-    <t>0.282</t>
-  </si>
-  <si>
-    <t>-0.888**</t>
-  </si>
-  <si>
-    <t>0.322</t>
-  </si>
-  <si>
-    <t>-0.420</t>
-  </si>
-  <si>
-    <t>0.268</t>
-  </si>
-  <si>
-    <t>Intercept</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>0.481</t>
-  </si>
-  <si>
-    <t>0.958*</t>
-  </si>
-  <si>
-    <t>0.401</t>
-  </si>
-  <si>
-    <t>-0.382</t>
-  </si>
-  <si>
-    <t>0.576</t>
-  </si>
-  <si>
-    <t>-0.852</t>
-  </si>
-  <si>
-    <t>0.686</t>
-  </si>
-  <si>
-    <t>1.756***</t>
-  </si>
-  <si>
-    <t>0.358</t>
-  </si>
-  <si>
-    <t>1.725***</t>
-  </si>
-  <si>
-    <t>0.389</t>
-  </si>
-  <si>
-    <t>0.984*</t>
-  </si>
-  <si>
-    <t>0.418</t>
-  </si>
-  <si>
-    <t>Cluster</t>
-  </si>
-  <si>
-    <t>Predictor</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>SE</t>
-  </si>
-  <si>
-    <t>OR</t>
-  </si>
-  <si>
-    <t>95% CI</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>Cluster 2 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[11.207, 3482.271]</t>
-  </si>
-  <si>
-    <t>&lt; .001</t>
-  </si>
-  <si>
-    <t>Cluster 3 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.591, 185.735]</t>
-  </si>
-  <si>
-    <t>0.109</t>
-  </si>
-  <si>
-    <t>Cluster 4 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.000, 0.001]</t>
-  </si>
-  <si>
-    <t>Cluster 5 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.000, 0.041]</t>
+    <t>[0.757, 2.482]</t>
+  </si>
+  <si>
+    <t>[0.844, 2.433]</t>
+  </si>
+  <si>
+    <t>0.182</t>
+  </si>
+  <si>
+    <t>[0.903, 2.915]</t>
+  </si>
+  <si>
+    <t>0.105</t>
+  </si>
+  <si>
+    <t>[2.259, 8.803]</t>
+  </si>
+  <si>
+    <t>[0.693, 3.709]</t>
+  </si>
+  <si>
+    <t>[1.244, 5.266]</t>
+  </si>
+  <si>
+    <t>0.011</t>
+  </si>
+  <si>
+    <t>[1.165, 3.574]</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>[0.804, 3.072]</t>
+  </si>
+  <si>
+    <t>0.186</t>
+  </si>
+  <si>
+    <t>[1.358, 4.472]</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>[0.240, 1.463]</t>
+  </si>
+  <si>
+    <t>0.257</t>
+  </si>
+  <si>
+    <t>[1.841, 8.394]</t>
+  </si>
+  <si>
+    <t>[0.399, 3.127]</t>
+  </si>
+  <si>
+    <t>0.832</t>
+  </si>
+  <si>
+    <t>[0.412, 4.094]</t>
+  </si>
+  <si>
+    <t>0.656</t>
+  </si>
+  <si>
+    <t>[1.455, 40.250]</t>
+  </si>
+  <si>
+    <t>0.016</t>
+  </si>
+  <si>
+    <t>[1.425, 41.992]</t>
+  </si>
+  <si>
+    <t>0.018</t>
+  </si>
+  <si>
+    <t>[1.728, 48.760]</t>
+  </si>
+  <si>
+    <t>[1.305, 40.127]</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>[2.572, 77.882]</t>
   </si>
   <si>
     <t>0.002</t>
   </si>
   <si>
-    <t>Cluster 6 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.166, 34.180]</t>
-  </si>
-  <si>
-    <t>Cluster 7 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.002, 1.129]</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>Cluster 8 vs. Cluster 1</t>
-  </si>
-  <si>
-    <t>[0.001, 1.305]</t>
-  </si>
-  <si>
-    <t>0.070</t>
-  </si>
-  <si>
-    <t>[0.613, 6.624]</t>
-  </si>
-  <si>
-    <t>0.248</t>
-  </si>
-  <si>
-    <t>[0.416, 5.229]</t>
-  </si>
-  <si>
-    <t>[0.296, 3.918]</t>
-  </si>
-  <si>
-    <t>0.910</t>
-  </si>
-  <si>
-    <t>[0.212, 5.021]</t>
-  </si>
-  <si>
-    <t>0.969</t>
-  </si>
-  <si>
-    <t>[0.425, 4.083]</t>
-  </si>
-  <si>
-    <t>0.632</t>
-  </si>
-  <si>
-    <t>[0.644, 6.556]</t>
-  </si>
-  <si>
-    <t>0.223</t>
-  </si>
-  <si>
-    <t>[1.284, 13.226]</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>[0.666, 4.272]</t>
-  </si>
-  <si>
-    <t>0.270</t>
-  </si>
-  <si>
-    <t>[0.284, 1.458]</t>
-  </si>
-  <si>
-    <t>0.291</t>
-  </si>
-  <si>
-    <t>[0.146, 0.567]</t>
-  </si>
-  <si>
-    <t>[1.154, 4.274]</t>
-  </si>
-  <si>
-    <t>[0.750, 2.670]</t>
-  </si>
-  <si>
-    <t>0.284</t>
-  </si>
-  <si>
-    <t>[0.210, 0.791]</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>[0.337, 1.351]</t>
-  </si>
-  <si>
-    <t>[0.529, 8.615]</t>
-  </si>
-  <si>
-    <t>[0.635, 7.680]</t>
-  </si>
-  <si>
-    <t>0.213</t>
-  </si>
-  <si>
-    <t>[2.094, 16.526]</t>
-  </si>
-  <si>
-    <t>[0.316, 2.718]</t>
-  </si>
-  <si>
-    <t>0.890</t>
-  </si>
-  <si>
-    <t>[0.773, 5.890]</t>
-  </si>
-  <si>
-    <t>0.143</t>
-  </si>
-  <si>
-    <t>[1.425, 11.245]</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>[0.637, 5.838]</t>
-  </si>
-  <si>
-    <t>0.245</t>
-  </si>
-  <si>
-    <t>[1.027, 16.213]</t>
-  </si>
-  <si>
-    <t>0.046</t>
-  </si>
-  <si>
-    <t>[0.636, 4.900]</t>
-  </si>
-  <si>
-    <t>0.275</t>
-  </si>
-  <si>
-    <t>[1.081, 5.145]</t>
-  </si>
-  <si>
-    <t>0.031</t>
-  </si>
-  <si>
-    <t>[0.673, 3.820]</t>
-  </si>
-  <si>
-    <t>0.286</t>
-  </si>
-  <si>
-    <t>[1.176, 6.447]</t>
-  </si>
-  <si>
-    <t>0.020</t>
-  </si>
-  <si>
-    <t>[0.746, 3.794]</t>
-  </si>
-  <si>
-    <t>0.210</t>
-  </si>
-  <si>
-    <t>[0.716, 4.501]</t>
-  </si>
-  <si>
-    <t>[0.375, 1.990]</t>
-  </si>
-  <si>
-    <t>0.731</t>
-  </si>
-  <si>
-    <t>[0.233, 0.855]</t>
-  </si>
-  <si>
-    <t>0.015</t>
-  </si>
-  <si>
-    <t>[0.534, 1.384]</t>
-  </si>
-  <si>
-    <t>0.534</t>
-  </si>
-  <si>
-    <t>[0.533, 1.494]</t>
-  </si>
-  <si>
-    <t>0.666</t>
-  </si>
-  <si>
-    <t>[0.562, 1.528]</t>
-  </si>
-  <si>
-    <t>0.767</t>
-  </si>
-  <si>
-    <t>[0.449, 1.207]</t>
-  </si>
-  <si>
-    <t>0.225</t>
-  </si>
-  <si>
-    <t>[0.350, 1.054]</t>
-  </si>
-  <si>
-    <t>0.076</t>
-  </si>
-  <si>
-    <t>[0.125, 0.638]</t>
-  </si>
-  <si>
-    <t>[0.311, 1.073]</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>[0.188, 0.549]</t>
-  </si>
-  <si>
-    <t>[0.187, 0.624]</t>
-  </si>
-  <si>
-    <t>[0.149, 0.479]</t>
-  </si>
-  <si>
-    <t>[0.185, 0.539]</t>
-  </si>
-  <si>
-    <t>[0.160, 0.551]</t>
-  </si>
-  <si>
-    <t>[0.110, 0.730]</t>
-  </si>
-  <si>
-    <t>[0.097, 0.685]</t>
-  </si>
-  <si>
-    <t>0.007</t>
-  </si>
-  <si>
-    <t>[0.327, 0.985]</t>
-  </si>
-  <si>
-    <t>0.044</t>
-  </si>
-  <si>
-    <t>[0.312, 1.090]</t>
-  </si>
-  <si>
-    <t>0.091</t>
-  </si>
-  <si>
-    <t>[0.349, 1.074]</t>
-  </si>
-  <si>
-    <t>0.087</t>
-  </si>
-  <si>
-    <t>[0.114, 0.425]</t>
-  </si>
-  <si>
-    <t>[0.241, 0.881]</t>
-  </si>
-  <si>
-    <t>0.019</t>
-  </si>
-  <si>
-    <t>[0.410, 1.383]</t>
-  </si>
-  <si>
-    <t>0.361</t>
-  </si>
-  <si>
-    <t>[0.239, 1.387]</t>
-  </si>
-  <si>
-    <t>0.219</t>
-  </si>
-  <si>
-    <t>[0.341, 0.898]</t>
-  </si>
-  <si>
-    <t>0.016</t>
-  </si>
-  <si>
-    <t>[0.312, 1.250]</t>
-  </si>
-  <si>
-    <t>0.184</t>
-  </si>
-  <si>
-    <t>[0.321, 0.970]</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>[0.219, 0.773]</t>
-  </si>
-  <si>
-    <t>[0.389, 1.111]</t>
-  </si>
-  <si>
-    <t>0.117</t>
-  </si>
-  <si>
-    <t>[0.392, 2.583]</t>
-  </si>
-  <si>
-    <t>0.989</t>
-  </si>
-  <si>
-    <t>[1.188, 5.720]</t>
-  </si>
-  <si>
-    <t>[0.221, 2.111]</t>
-  </si>
-  <si>
-    <t>0.508</t>
-  </si>
-  <si>
-    <t>[0.111, 1.637]</t>
-  </si>
-  <si>
-    <t>0.214</t>
-  </si>
-  <si>
-    <t>[2.870, 11.678]</t>
-  </si>
-  <si>
-    <t>[2.618, 12.030]</t>
-  </si>
-  <si>
-    <t>[1.179, 6.070]</t>
+    <t>[1.797, 56.588]</t>
+  </si>
+  <si>
+    <t>[0.375, 43.704]</t>
+  </si>
+  <si>
+    <t>[8.034, 779.241]</t>
+  </si>
+  <si>
+    <t>[11.089, 1105.486]</t>
+  </si>
+  <si>
+    <t>[45.433, 4220.716]</t>
+  </si>
+  <si>
+    <t>[15.056, 1471.798]</t>
+  </si>
+  <si>
+    <t>[4.063, 445.003]</t>
+  </si>
+  <si>
+    <t>[3.474, 398.856]</t>
+  </si>
+  <si>
+    <t>[2.271, 317.221]</t>
   </si>
   <si>
     <t>N</t>
@@ -1360,110 +1363,110 @@
         <v>35</v>
       </c>
       <c r="G3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H3" t="s">
         <v>36</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>37</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>38</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>39</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>40</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="M3" t="s">
+      <c r="N3" t="s">
         <v>42</v>
       </c>
-      <c r="N3" t="s">
+      <c r="O3" t="s">
         <v>43</v>
-      </c>
-      <c r="O3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
         <v>45</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>46</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>47</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>48</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>49</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>50</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>51</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>52</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>53</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>54</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>55</v>
       </c>
-      <c r="L4" t="s">
+      <c r="M4" t="s">
         <v>56</v>
       </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>57</v>
       </c>
-      <c r="N4" t="s">
+      <c r="O4" t="s">
         <v>58</v>
-      </c>
-      <c r="O4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" t="s">
         <v>60</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>61</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>62</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>63</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>64</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>65</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>66</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>67</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>68</v>
-      </c>
-      <c r="J5" t="s">
-        <v>61</v>
       </c>
       <c r="K5" t="s">
         <v>69</v>
@@ -1472,51 +1475,51 @@
         <v>70</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="N5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L6" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="M6" t="s">
         <v>85</v>
@@ -1557,210 +1560,210 @@
         <v>96</v>
       </c>
       <c r="J7" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="K7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="L7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" t="s">
+        <v>108</v>
+      </c>
+      <c r="G8" t="s">
         <v>104</v>
       </c>
-      <c r="E8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F8" t="s">
-        <v>106</v>
-      </c>
-      <c r="G8" t="s">
-        <v>107</v>
-      </c>
       <c r="H8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D9" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="E9" t="s">
-        <v>119</v>
+        <v>61</v>
       </c>
       <c r="F9" t="s">
         <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="H9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I10" t="s">
-        <v>59</v>
+        <v>138</v>
       </c>
       <c r="J10" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="K10" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="M10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="I11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="J11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="K11" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L11" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M11" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O11" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1775,163 +1778,163 @@
   <sheetData>
     <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2">
-        <v>5.286</v>
+        <v>10.188</v>
       </c>
       <c r="D2">
-        <v>1.464</v>
+        <v>4.477</v>
       </c>
       <c r="E2">
-        <v>197.552</v>
+        <v>26582.277</v>
       </c>
       <c r="F2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3">
-        <v>2.349</v>
+        <v>15.73</v>
       </c>
       <c r="D3">
-        <v>1.467</v>
+        <v>4.545</v>
       </c>
       <c r="E3">
-        <v>10.475</v>
+        <v>6783474.556</v>
       </c>
       <c r="F3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="G3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4">
-        <v>-11.372</v>
+        <v>18.241</v>
       </c>
       <c r="D4">
-        <v>2.371</v>
+        <v>4.453</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>83553691.905</v>
       </c>
       <c r="F4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" t="s">
         <v>172</v>
-      </c>
-      <c r="G4" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5">
-        <v>-8.968</v>
+        <v>19.112</v>
       </c>
       <c r="D5">
-        <v>2.943</v>
+        <v>4.502</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>199634749.025</v>
       </c>
       <c r="F5" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="G5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6">
-        <v>0.868</v>
+        <v>18.522</v>
       </c>
       <c r="D6">
-        <v>1.359</v>
+        <v>4.587</v>
       </c>
       <c r="E6">
-        <v>2.382</v>
+        <v>110662988.366</v>
       </c>
       <c r="F6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G6" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7">
-        <v>-3.042</v>
+        <v>23.562</v>
       </c>
       <c r="D7">
-        <v>1.614</v>
+        <v>4.524</v>
       </c>
       <c r="E7">
-        <v>0.048</v>
+        <v>17094113475.644</v>
       </c>
       <c r="F7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1942,13 +1945,13 @@
         <v>15</v>
       </c>
       <c r="C8">
-        <v>-3.203</v>
+        <v>15.922</v>
       </c>
       <c r="D8">
-        <v>1.77</v>
+        <v>4.993</v>
       </c>
       <c r="E8">
-        <v>0.041</v>
+        <v>8219336.122</v>
       </c>
       <c r="F8" t="s">
         <v>182</v>
@@ -1959,19 +1962,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
       <c r="C9">
-        <v>0.701</v>
+        <v>-0.653</v>
       </c>
       <c r="D9">
-        <v>0.607</v>
+        <v>0.63</v>
       </c>
       <c r="E9">
-        <v>2.016</v>
+        <v>0.52</v>
       </c>
       <c r="F9" t="s">
         <v>184</v>
@@ -1982,117 +1985,117 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
       <c r="C10">
-        <v>0.388</v>
+        <v>0.22</v>
       </c>
       <c r="D10">
-        <v>0.646</v>
+        <v>0.642</v>
       </c>
       <c r="E10">
-        <v>1.474</v>
+        <v>1.246</v>
       </c>
       <c r="F10" t="s">
         <v>186</v>
       </c>
       <c r="G10" t="s">
-        <v>68</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11">
-        <v>0.074</v>
+        <v>-0.318</v>
       </c>
       <c r="D11">
-        <v>0.659</v>
+        <v>0.63</v>
       </c>
       <c r="E11">
-        <v>1.077</v>
+        <v>0.728</v>
       </c>
       <c r="F11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12">
-        <v>0.032</v>
+        <v>-0.102</v>
       </c>
       <c r="D12">
-        <v>0.8070000000000001</v>
+        <v>0.655</v>
       </c>
       <c r="E12">
-        <v>1.033</v>
+        <v>0.903</v>
       </c>
       <c r="F12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G12" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13">
-        <v>0.276</v>
+        <v>-0.77</v>
       </c>
       <c r="D13">
-        <v>0.577</v>
+        <v>0.776</v>
       </c>
       <c r="E13">
-        <v>1.318</v>
+        <v>0.463</v>
       </c>
       <c r="F13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
       <c r="C14">
-        <v>0.72</v>
+        <v>-0.136</v>
       </c>
       <c r="D14">
-        <v>0.592</v>
+        <v>0.671</v>
       </c>
       <c r="E14">
-        <v>2.054</v>
+        <v>0.873</v>
       </c>
       <c r="F14" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G14" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2103,157 +2106,157 @@
         <v>30</v>
       </c>
       <c r="C15">
-        <v>1.416</v>
+        <v>-0.302</v>
       </c>
       <c r="D15">
-        <v>0.595</v>
+        <v>0.903</v>
       </c>
       <c r="E15">
-        <v>4.121</v>
+        <v>0.739</v>
       </c>
       <c r="F15" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16">
-        <v>0.523</v>
+        <v>-0.254</v>
       </c>
       <c r="D16">
-        <v>0.474</v>
+        <v>0.276</v>
       </c>
       <c r="E16">
-        <v>1.687</v>
+        <v>0.776</v>
       </c>
       <c r="F16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G16" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17">
-        <v>-0.44</v>
+        <v>-0.051</v>
       </c>
       <c r="D17">
-        <v>0.417</v>
+        <v>0.343</v>
       </c>
       <c r="E17">
-        <v>0.644</v>
+        <v>0.95</v>
       </c>
       <c r="F17" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G17" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18">
-        <v>-1.245</v>
+        <v>1.543</v>
       </c>
       <c r="D18">
-        <v>0.346</v>
+        <v>0.288</v>
       </c>
       <c r="E18">
-        <v>0.288</v>
+        <v>4.679</v>
       </c>
       <c r="F18" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="G18" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19">
-        <v>0.798</v>
+        <v>0.101</v>
       </c>
       <c r="D19">
-        <v>0.334</v>
+        <v>0.351</v>
       </c>
       <c r="E19">
-        <v>2.221</v>
+        <v>1.106</v>
       </c>
       <c r="F19" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G19" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>0.347</v>
+        <v>1.035</v>
       </c>
       <c r="D20">
-        <v>0.324</v>
+        <v>0.397</v>
       </c>
       <c r="E20">
-        <v>1.415</v>
+        <v>2.815</v>
       </c>
       <c r="F20" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G20" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21">
-        <v>-0.897</v>
+        <v>1.724</v>
       </c>
       <c r="D21">
-        <v>0.338</v>
+        <v>0.471</v>
       </c>
       <c r="E21">
-        <v>0.408</v>
+        <v>5.607</v>
       </c>
       <c r="F21" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="G21" t="s">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2261,160 +2264,160 @@
         <v>181</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22">
-        <v>-0.393</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D22">
-        <v>0.354</v>
+        <v>0.466</v>
       </c>
       <c r="E22">
-        <v>0.675</v>
+        <v>1.758</v>
       </c>
       <c r="F22" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G22" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C23">
-        <v>0.758</v>
+        <v>-0.258</v>
       </c>
       <c r="D23">
-        <v>0.712</v>
+        <v>0.342</v>
       </c>
       <c r="E23">
-        <v>2.134</v>
+        <v>0.773</v>
       </c>
       <c r="F23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="G23" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24">
-        <v>0.792</v>
+        <v>-0.755</v>
       </c>
       <c r="D24">
-        <v>0.636</v>
+        <v>0.433</v>
       </c>
       <c r="E24">
-        <v>2.208</v>
+        <v>0.47</v>
       </c>
       <c r="F24" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G24" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C25">
-        <v>1.772</v>
+        <v>-1.768</v>
       </c>
       <c r="D25">
-        <v>0.527</v>
+        <v>0.379</v>
       </c>
       <c r="E25">
-        <v>5.883</v>
+        <v>0.171</v>
       </c>
       <c r="F25" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G25" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C26">
-        <v>-0.076</v>
+        <v>-0.592</v>
       </c>
       <c r="D26">
-        <v>0.549</v>
+        <v>0.438</v>
       </c>
       <c r="E26">
-        <v>0.927</v>
+        <v>0.553</v>
       </c>
       <c r="F26" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G26" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C27">
-        <v>0.758</v>
+        <v>-1.965</v>
       </c>
       <c r="D27">
-        <v>0.518</v>
+        <v>0.571</v>
       </c>
       <c r="E27">
-        <v>2.134</v>
+        <v>0.14</v>
       </c>
       <c r="F27" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G27" t="s">
-        <v>215</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C28">
-        <v>1.387</v>
+        <v>-1.277</v>
       </c>
       <c r="D28">
-        <v>0.527</v>
+        <v>0.624</v>
       </c>
       <c r="E28">
-        <v>4.003</v>
+        <v>0.279</v>
       </c>
       <c r="F28" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G28" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -2422,160 +2425,160 @@
         <v>181</v>
       </c>
       <c r="B29" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C29">
-        <v>0.657</v>
+        <v>-1.189</v>
       </c>
       <c r="D29">
-        <v>0.5649999999999999</v>
+        <v>0.644</v>
       </c>
       <c r="E29">
-        <v>1.929</v>
+        <v>0.305</v>
       </c>
       <c r="F29" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="G29" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C30">
-        <v>1.406</v>
+        <v>0.119</v>
       </c>
       <c r="D30">
-        <v>0.704</v>
+        <v>0.279</v>
       </c>
       <c r="E30">
-        <v>4.08</v>
+        <v>1.126</v>
       </c>
       <c r="F30" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="G30" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C31">
-        <v>0.5679999999999999</v>
+        <v>-0.189</v>
       </c>
       <c r="D31">
-        <v>0.521</v>
+        <v>0.372</v>
       </c>
       <c r="E31">
-        <v>1.765</v>
+        <v>0.828</v>
       </c>
       <c r="F31" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="G31" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B32" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C32">
-        <v>0.858</v>
+        <v>-0.074</v>
       </c>
       <c r="D32">
-        <v>0.398</v>
+        <v>0.32</v>
       </c>
       <c r="E32">
-        <v>2.358</v>
+        <v>0.929</v>
       </c>
       <c r="F32" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="G32" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C33">
-        <v>0.472</v>
+        <v>-0.138</v>
       </c>
       <c r="D33">
-        <v>0.443</v>
+        <v>0.394</v>
       </c>
       <c r="E33">
-        <v>1.603</v>
+        <v>0.871</v>
       </c>
       <c r="F33" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="G33" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B34" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C34">
-        <v>1.013</v>
+        <v>-0.762</v>
       </c>
       <c r="D34">
-        <v>0.434</v>
+        <v>0.452</v>
       </c>
       <c r="E34">
-        <v>2.754</v>
+        <v>0.467</v>
       </c>
       <c r="F34" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="G34" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B35" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C35">
-        <v>0.52</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="D35">
-        <v>0.415</v>
+        <v>0.653</v>
       </c>
       <c r="E35">
-        <v>1.682</v>
+        <v>1.758</v>
       </c>
       <c r="F35" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="G35" t="s">
-        <v>231</v>
+        <v>125</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2583,160 +2586,160 @@
         <v>181</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C36">
-        <v>0.585</v>
+        <v>-0.577</v>
       </c>
       <c r="D36">
-        <v>0.469</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="E36">
-        <v>1.795</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="F36" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G36" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B37" t="s">
         <v>88</v>
       </c>
       <c r="C37">
-        <v>-0.147</v>
+        <v>0.102</v>
       </c>
       <c r="D37">
-        <v>0.426</v>
+        <v>0.179</v>
       </c>
       <c r="E37">
-        <v>0.863</v>
+        <v>1.107</v>
       </c>
       <c r="F37" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="G37" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s">
         <v>88</v>
       </c>
       <c r="C38">
-        <v>-0.8070000000000001</v>
+        <v>-0.182</v>
       </c>
       <c r="D38">
-        <v>0.332</v>
+        <v>0.232</v>
       </c>
       <c r="E38">
-        <v>0.446</v>
+        <v>0.834</v>
       </c>
       <c r="F38" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="G38" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
         <v>88</v>
       </c>
       <c r="C39">
-        <v>-0.151</v>
+        <v>0.13</v>
       </c>
       <c r="D39">
-        <v>0.243</v>
+        <v>0.197</v>
       </c>
       <c r="E39">
-        <v>0.86</v>
+        <v>1.139</v>
       </c>
       <c r="F39" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G39" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
         <v>88</v>
       </c>
       <c r="C40">
-        <v>-0.114</v>
+        <v>-0.097</v>
       </c>
       <c r="D40">
-        <v>0.263</v>
+        <v>0.249</v>
       </c>
       <c r="E40">
-        <v>0.892</v>
+        <v>0.908</v>
       </c>
       <c r="F40" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="G40" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B41" t="s">
         <v>88</v>
       </c>
       <c r="C41">
-        <v>-0.076</v>
+        <v>0.269</v>
       </c>
       <c r="D41">
-        <v>0.255</v>
+        <v>0.278</v>
       </c>
       <c r="E41">
-        <v>0.927</v>
+        <v>1.309</v>
       </c>
       <c r="F41" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="G41" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B42" t="s">
         <v>88</v>
       </c>
       <c r="C42">
-        <v>-0.306</v>
+        <v>0.235</v>
       </c>
       <c r="D42">
-        <v>0.252</v>
+        <v>0.395</v>
       </c>
       <c r="E42">
-        <v>0.736</v>
+        <v>1.265</v>
       </c>
       <c r="F42" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="G42" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -2747,157 +2750,157 @@
         <v>88</v>
       </c>
       <c r="C43">
-        <v>-0.498</v>
+        <v>-0.411</v>
       </c>
       <c r="D43">
-        <v>0.281</v>
+        <v>0.34</v>
       </c>
       <c r="E43">
-        <v>0.608</v>
+        <v>0.663</v>
       </c>
       <c r="F43" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G43" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B44" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44">
-        <v>-1.266</v>
+        <v>0.27</v>
       </c>
       <c r="D44">
-        <v>0.417</v>
+        <v>0.254</v>
       </c>
       <c r="E44">
-        <v>0.282</v>
+        <v>1.31</v>
       </c>
       <c r="F44" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G44" t="s">
-        <v>175</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C45">
-        <v>-0.549</v>
+        <v>0.315</v>
       </c>
       <c r="D45">
-        <v>0.316</v>
+        <v>0.303</v>
       </c>
       <c r="E45">
-        <v>0.578</v>
+        <v>1.37</v>
       </c>
       <c r="F45" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="G45" t="s">
-        <v>249</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C46">
-        <v>-1.135</v>
+        <v>0.36</v>
       </c>
       <c r="D46">
-        <v>0.273</v>
+        <v>0.27</v>
       </c>
       <c r="E46">
-        <v>0.321</v>
+        <v>1.433</v>
       </c>
       <c r="F46" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G46" t="s">
-        <v>167</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C47">
-        <v>-1.075</v>
+        <v>0.484</v>
       </c>
       <c r="D47">
-        <v>0.308</v>
+        <v>0.299</v>
       </c>
       <c r="E47">
-        <v>0.341</v>
+        <v>1.623</v>
       </c>
       <c r="F47" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="G47" t="s">
-        <v>167</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48">
-        <v>-1.32</v>
+        <v>1.495</v>
       </c>
       <c r="D48">
-        <v>0.298</v>
+        <v>0.347</v>
       </c>
       <c r="E48">
-        <v>0.267</v>
+        <v>4.459</v>
       </c>
       <c r="F48" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C49">
-        <v>-1.153</v>
+        <v>0.472</v>
       </c>
       <c r="D49">
-        <v>0.273</v>
+        <v>0.428</v>
       </c>
       <c r="E49">
-        <v>0.316</v>
+        <v>1.603</v>
       </c>
       <c r="F49" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="G49" t="s">
-        <v>167</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2905,160 +2908,160 @@
         <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C50">
-        <v>-1.214</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="D50">
-        <v>0.315</v>
+        <v>0.368</v>
       </c>
       <c r="E50">
-        <v>0.297</v>
+        <v>2.56</v>
       </c>
       <c r="F50" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="G50" t="s">
-        <v>167</v>
+        <v>259</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B51" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C51">
-        <v>-1.263</v>
+        <v>0.713</v>
       </c>
       <c r="D51">
-        <v>0.484</v>
+        <v>0.286</v>
       </c>
       <c r="E51">
-        <v>0.283</v>
+        <v>2.04</v>
       </c>
       <c r="F51" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="G51" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52">
-        <v>-1.355</v>
+        <v>0.452</v>
       </c>
       <c r="D52">
-        <v>0.498</v>
+        <v>0.342</v>
       </c>
       <c r="E52">
-        <v>0.258</v>
+        <v>1.571</v>
       </c>
       <c r="F52" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="G52" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53">
-        <v>-0.5659999999999999</v>
+        <v>0.902</v>
       </c>
       <c r="D53">
-        <v>0.281</v>
+        <v>0.304</v>
       </c>
       <c r="E53">
-        <v>0.5679999999999999</v>
+        <v>2.465</v>
       </c>
       <c r="F53" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="G53" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C54">
-        <v>-0.539</v>
+        <v>-0.523</v>
       </c>
       <c r="D54">
-        <v>0.319</v>
+        <v>0.461</v>
       </c>
       <c r="E54">
-        <v>0.583</v>
+        <v>0.593</v>
       </c>
       <c r="F54" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="G54" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C55">
-        <v>-0.491</v>
+        <v>1.369</v>
       </c>
       <c r="D55">
-        <v>0.287</v>
+        <v>0.387</v>
       </c>
       <c r="E55">
-        <v>0.612</v>
+        <v>3.931</v>
       </c>
       <c r="F55" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="G55" t="s">
-        <v>263</v>
+        <v>172</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C56">
-        <v>-1.512</v>
+        <v>0.111</v>
       </c>
       <c r="D56">
-        <v>0.335</v>
+        <v>0.525</v>
       </c>
       <c r="E56">
-        <v>0.22</v>
+        <v>1.117</v>
       </c>
       <c r="F56" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G56" t="s">
-        <v>167</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3066,160 +3069,160 @@
         <v>181</v>
       </c>
       <c r="B57" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C57">
-        <v>-0.775</v>
+        <v>0.261</v>
       </c>
       <c r="D57">
-        <v>0.331</v>
+        <v>0.586</v>
       </c>
       <c r="E57">
-        <v>0.461</v>
+        <v>1.298</v>
       </c>
       <c r="F57" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="G57" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C58">
-        <v>-0.283</v>
+        <v>2.035</v>
       </c>
       <c r="D58">
-        <v>0.31</v>
+        <v>0.847</v>
       </c>
       <c r="E58">
-        <v>0.754</v>
+        <v>7.652</v>
       </c>
       <c r="F58" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="G58" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B59" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C59">
-        <v>-0.553</v>
+        <v>2.046</v>
       </c>
       <c r="D59">
-        <v>0.449</v>
+        <v>0.863</v>
       </c>
       <c r="E59">
-        <v>0.575</v>
+        <v>7.737</v>
       </c>
       <c r="F59" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="G59" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C60">
-        <v>-0.592</v>
+        <v>2.217</v>
       </c>
       <c r="D60">
-        <v>0.247</v>
+        <v>0.852</v>
       </c>
       <c r="E60">
-        <v>0.553</v>
+        <v>9.18</v>
       </c>
       <c r="F60" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="G60" t="s">
-        <v>272</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C61">
-        <v>-0.471</v>
+        <v>1.979</v>
       </c>
       <c r="D61">
-        <v>0.354</v>
+        <v>0.874</v>
       </c>
       <c r="E61">
-        <v>0.624</v>
+        <v>7.236</v>
       </c>
       <c r="F61" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="G61" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B62" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C62">
-        <v>-0.583</v>
+        <v>2.65</v>
       </c>
       <c r="D62">
-        <v>0.282</v>
+        <v>0.87</v>
       </c>
       <c r="E62">
-        <v>0.5580000000000001</v>
+        <v>14.154</v>
       </c>
       <c r="F62" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G62" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B63" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C63">
-        <v>-0.888</v>
+        <v>2.311</v>
       </c>
       <c r="D63">
-        <v>0.322</v>
+        <v>0.88</v>
       </c>
       <c r="E63">
-        <v>0.411</v>
+        <v>10.085</v>
       </c>
       <c r="F63" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="G63" t="s">
-        <v>144</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3227,160 +3230,160 @@
         <v>181</v>
       </c>
       <c r="B64" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C64">
-        <v>-0.42</v>
+        <v>1.398</v>
       </c>
       <c r="D64">
-        <v>0.268</v>
+        <v>1.214</v>
       </c>
       <c r="E64">
-        <v>0.657</v>
+        <v>4.047</v>
       </c>
       <c r="F64" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G64" t="s">
-        <v>279</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C65">
-        <v>0.006</v>
+        <v>4.371</v>
       </c>
       <c r="D65">
-        <v>0.481</v>
+        <v>1.167</v>
       </c>
       <c r="E65">
-        <v>1.006</v>
+        <v>79.123</v>
       </c>
       <c r="F65" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G65" t="s">
-        <v>281</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C66">
-        <v>0.958</v>
+        <v>4.707</v>
       </c>
       <c r="D66">
-        <v>0.401</v>
+        <v>1.174</v>
       </c>
       <c r="E66">
-        <v>2.606</v>
+        <v>110.72</v>
       </c>
       <c r="F66" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="G66" t="s">
-        <v>196</v>
+        <v>172</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B67" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C67">
-        <v>-0.382</v>
+        <v>6.082</v>
       </c>
       <c r="D67">
-        <v>0.576</v>
+        <v>1.156</v>
       </c>
       <c r="E67">
-        <v>0.6820000000000001</v>
+        <v>437.904</v>
       </c>
       <c r="F67" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G67" t="s">
-        <v>284</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B68" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C68">
-        <v>-0.852</v>
+        <v>5.003</v>
       </c>
       <c r="D68">
-        <v>0.6860000000000001</v>
+        <v>1.169</v>
       </c>
       <c r="E68">
-        <v>0.427</v>
+        <v>148.859</v>
       </c>
       <c r="F68" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="G68" t="s">
-        <v>286</v>
+        <v>172</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C69">
-        <v>1.756</v>
+        <v>3.75</v>
       </c>
       <c r="D69">
-        <v>0.358</v>
+        <v>1.198</v>
       </c>
       <c r="E69">
-        <v>5.789</v>
+        <v>42.521</v>
       </c>
       <c r="F69" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G69" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
     </row>
     <row r="70" spans="1:7">
       <c r="A70" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B70" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C70">
-        <v>1.725</v>
+        <v>3.617</v>
       </c>
       <c r="D70">
-        <v>0.389</v>
+        <v>1.21</v>
       </c>
       <c r="E70">
-        <v>5.613</v>
+        <v>37.226</v>
       </c>
       <c r="F70" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G70" t="s">
-        <v>167</v>
+        <v>265</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3388,22 +3391,22 @@
         <v>181</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C71">
-        <v>0.984</v>
+        <v>3.29</v>
       </c>
       <c r="D71">
-        <v>0.418</v>
+        <v>1.26</v>
       </c>
       <c r="E71">
-        <v>2.675</v>
+        <v>26.843</v>
       </c>
       <c r="F71" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G71" t="s">
-        <v>266</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3418,16 +3421,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3435,10 +3438,10 @@
         <v>719</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C2">
-        <v>2110.55</v>
+        <v>2041.85</v>
       </c>
       <c r="D2" t="b">
         <v>1</v>
